--- a/Dashboard_PR/ข้อมูลดิบ/เรื่องร้องเรียน/PR_69-03.xlsx
+++ b/Dashboard_PR/ข้อมูลดิบ/เรื่องร้องเรียน/PR_69-03.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="90">
   <si>
     <t>กปภ.ข</t>
   </si>
@@ -74,196 +74,208 @@
     <t>ชลบุรี</t>
   </si>
   <si>
-    <t>138,099</t>
+    <t>138,238</t>
   </si>
   <si>
     <t> 0</t>
   </si>
   <si>
+    <t> 1</t>
+  </si>
+  <si>
+    <t> 2</t>
+  </si>
+  <si>
+    <t>1,323</t>
+  </si>
+  <si>
+    <t>บ้านบึง</t>
+  </si>
+  <si>
+    <t>49,250</t>
+  </si>
+  <si>
+    <t> 7</t>
+  </si>
+  <si>
+    <t> 3</t>
+  </si>
+  <si>
+    <t>พนัสนิคม</t>
+  </si>
+  <si>
+    <t>65,664</t>
+  </si>
+  <si>
+    <t>ศรีราชา</t>
+  </si>
+  <si>
+    <t>55,666</t>
+  </si>
+  <si>
+    <t>แหลมฉบัง</t>
+  </si>
+  <si>
+    <t>68,341</t>
+  </si>
+  <si>
+    <t>พัทยา</t>
+  </si>
+  <si>
+    <t>116,773</t>
+  </si>
+  <si>
+    <t>2,282</t>
+  </si>
+  <si>
+    <t>ฉะเชิงเทรา</t>
+  </si>
+  <si>
+    <t>33,818</t>
+  </si>
+  <si>
+    <t> 6</t>
+  </si>
+  <si>
+    <t>บางปะกง</t>
+  </si>
+  <si>
+    <t>36,647</t>
+  </si>
+  <si>
+    <t> 4</t>
+  </si>
+  <si>
+    <t>บางคล้า</t>
+  </si>
+  <si>
+    <t>69,468</t>
+  </si>
+  <si>
+    <t> 8</t>
+  </si>
+  <si>
+    <t>พนมสารคาม</t>
+  </si>
+  <si>
+    <t>30,632</t>
+  </si>
+  <si>
+    <t>ระยอง</t>
+  </si>
+  <si>
+    <t>89,248</t>
+  </si>
+  <si>
+    <t>บ้านฉาง</t>
+  </si>
+  <si>
+    <t>113,576</t>
+  </si>
+  <si>
+    <t> 5</t>
+  </si>
+  <si>
+    <t>1,557</t>
+  </si>
+  <si>
+    <t>ปากน้ำประแสร์</t>
+  </si>
+  <si>
+    <t>19,466</t>
+  </si>
+  <si>
+    <t>จันทบุรี</t>
+  </si>
+  <si>
+    <t>65,819</t>
+  </si>
+  <si>
+    <t>1,619</t>
+  </si>
+  <si>
+    <t>ขลุง</t>
+  </si>
+  <si>
+    <t>14,667</t>
+  </si>
+  <si>
+    <t>ตราด</t>
+  </si>
+  <si>
+    <t>29,812</t>
+  </si>
+  <si>
+    <t>คลองใหญ่</t>
+  </si>
+  <si>
+    <t>4,734</t>
+  </si>
+  <si>
+    <t>สระแก้ว</t>
+  </si>
+  <si>
+    <t>15,046</t>
+  </si>
+  <si>
+    <t>วัฒนานคร</t>
+  </si>
+  <si>
+    <t>5,450</t>
+  </si>
+  <si>
     <t> 9</t>
   </si>
   <si>
-    <t> 1</t>
-  </si>
-  <si>
-    <t>บ้านบึง</t>
-  </si>
-  <si>
-    <t>49,082</t>
-  </si>
-  <si>
-    <t> 6</t>
-  </si>
-  <si>
-    <t> 2</t>
-  </si>
-  <si>
-    <t>พนัสนิคม</t>
-  </si>
-  <si>
-    <t>65,377</t>
-  </si>
-  <si>
-    <t> 3</t>
-  </si>
-  <si>
-    <t> 5</t>
-  </si>
-  <si>
-    <t> 7</t>
-  </si>
-  <si>
-    <t>ศรีราชา</t>
-  </si>
-  <si>
-    <t>55,529</t>
-  </si>
-  <si>
-    <t>แหลมฉบัง</t>
-  </si>
-  <si>
-    <t>68,222</t>
-  </si>
-  <si>
-    <t> 8</t>
-  </si>
-  <si>
-    <t>พัทยา</t>
-  </si>
-  <si>
-    <t>116,381</t>
-  </si>
-  <si>
-    <t>1,073</t>
-  </si>
-  <si>
-    <t>ฉะเชิงเทรา</t>
-  </si>
-  <si>
-    <t>33,746</t>
-  </si>
-  <si>
-    <t>บางปะกง</t>
-  </si>
-  <si>
-    <t>36,570</t>
-  </si>
-  <si>
-    <t>บางคล้า</t>
-  </si>
-  <si>
-    <t>69,272</t>
-  </si>
-  <si>
-    <t>พนมสารคาม</t>
-  </si>
-  <si>
-    <t>30,499</t>
-  </si>
-  <si>
-    <t>ระยอง</t>
-  </si>
-  <si>
-    <t>89,087</t>
-  </si>
-  <si>
-    <t>บ้านฉาง</t>
-  </si>
-  <si>
-    <t>112,659</t>
-  </si>
-  <si>
-    <t> 4</t>
-  </si>
-  <si>
-    <t>ปากน้ำประแสร์</t>
-  </si>
-  <si>
-    <t>19,412</t>
-  </si>
-  <si>
-    <t>จันทบุรี</t>
-  </si>
-  <si>
-    <t>64,686</t>
-  </si>
-  <si>
-    <t>ขลุง</t>
-  </si>
-  <si>
-    <t>14,655</t>
-  </si>
-  <si>
-    <t>ตราด</t>
-  </si>
-  <si>
-    <t>29,751</t>
-  </si>
-  <si>
-    <t>คลองใหญ่</t>
-  </si>
-  <si>
-    <t>4,711</t>
-  </si>
-  <si>
-    <t>สระแก้ว</t>
-  </si>
-  <si>
-    <t>15,018</t>
-  </si>
-  <si>
-    <t>วัฒนานคร</t>
-  </si>
-  <si>
-    <t>5,428</t>
-  </si>
-  <si>
     <t>อรัญประเทศ</t>
   </si>
   <si>
-    <t>19,985</t>
+    <t>20,071</t>
   </si>
   <si>
     <t>ปราจีนบุรี</t>
   </si>
   <si>
-    <t>42,472</t>
+    <t>42,772</t>
   </si>
   <si>
     <t>กบินทร์บุรี</t>
   </si>
   <si>
-    <t>13,635</t>
+    <t>13,657</t>
   </si>
   <si>
     <t>รวม เขต 1</t>
   </si>
   <si>
-    <t>1,094,276</t>
-  </si>
-  <si>
-    <t>2,061</t>
-  </si>
-  <si>
-    <t>1,123</t>
-  </si>
-  <si>
-    <t>1,288</t>
-  </si>
-  <si>
-    <t>1,287</t>
-  </si>
-  <si>
-    <t>5,985</t>
-  </si>
-  <si>
-    <t>5,984</t>
+    <t>1,098,815</t>
+  </si>
+  <si>
+    <t>2,214</t>
+  </si>
+  <si>
+    <t>4,593</t>
+  </si>
+  <si>
+    <t>2,885</t>
+  </si>
+  <si>
+    <t>3,203</t>
+  </si>
+  <si>
+    <t>3,201</t>
+  </si>
+  <si>
+    <t>13,910</t>
+  </si>
+  <si>
+    <t>13,908</t>
   </si>
   <si>
     <t>รวมทั้งหมด</t>
   </si>
   <si>
-    <t>GUI_019 วันเวลาพิมพ์: 13/03/2569 12:02:47</t>
+    <t>GUI_019 วันเวลาพิมพ์: 02/04/2569 07:42:43</t>
   </si>
   <si>
     <t>รายงานการร้องเรียนจากลูกค้าจำเเนกตามด้านการร้องเรียน</t>
@@ -703,7 +715,7 @@
     <col min="2" max="2" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="6.998" bestFit="true" customWidth="true" style="0"/>
@@ -733,7 +745,7 @@
     <col min="32" max="32" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="33" max="33" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="34" max="34" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="36" max="36" width="11.569" bestFit="true" customWidth="true" style="0"/>
     <col min="37" max="37" width="49.417" bestFit="true" customWidth="true" style="0"/>
     <col min="38" max="38" width="9.10" bestFit="true" style="0"/>
@@ -742,7 +754,7 @@
     <row r="1" spans="1:38" customHeight="1" ht="30">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
@@ -772,7 +784,7 @@
     <row r="2" spans="1:38">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -802,7 +814,7 @@
     <row r="3" spans="1:38">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -831,7 +843,7 @@
     </row>
     <row r="4" spans="1:38">
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1019,67 +1031,67 @@
         <v>19</v>
       </c>
       <c r="D7" s="5">
-        <v>2.22</v>
+        <v>4.76</v>
       </c>
       <c r="E7" s="5">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="F7" s="5">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="5">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="I7" s="5">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K7" s="5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L7" s="5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>21</v>
+      <c r="N7" s="5">
+        <v>29</v>
+      </c>
+      <c r="O7" s="5">
+        <v>29</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="T7" s="5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="U7" s="5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W7" s="5">
-        <v>149</v>
+        <v>407</v>
       </c>
       <c r="X7" s="5">
-        <v>149</v>
+        <v>407</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>20</v>
@@ -1094,10 +1106,10 @@
         <v>20</v>
       </c>
       <c r="AC7" s="5">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="AD7" s="5">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="AE7" s="5" t="s">
         <v>20</v>
@@ -1111,11 +1123,11 @@
       <c r="AH7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AI7" s="5">
-        <v>580</v>
-      </c>
-      <c r="AJ7" s="5">
-        <v>580</v>
+      <c r="AI7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ7" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>20</v>
@@ -1124,37 +1136,37 @@
     <row r="8" spans="1:38">
       <c r="A8" s="2"/>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="5">
-        <v>4.05</v>
+        <v>10.01</v>
       </c>
       <c r="E8" s="5">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="F8" s="5">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="5">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="I8" s="5">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>25</v>
+      <c r="K8" s="5">
+        <v>10</v>
+      </c>
+      <c r="L8" s="5">
+        <v>10</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>20</v>
@@ -1178,40 +1190,40 @@
         <v>20</v>
       </c>
       <c r="T8" s="5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="U8" s="5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W8" s="5">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="X8" s="5">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC8" s="5">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="AD8" s="5">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="AE8" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF8" s="5" t="s">
         <v>20</v>
@@ -1223,58 +1235,58 @@
         <v>20</v>
       </c>
       <c r="AI8" s="5">
-        <v>336</v>
+        <v>774</v>
       </c>
       <c r="AJ8" s="5">
-        <v>336</v>
+        <v>773</v>
       </c>
       <c r="AK8" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:38">
       <c r="A9" s="2"/>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5">
-        <v>0.87</v>
+        <v>2.07</v>
       </c>
       <c r="E9" s="5">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F9" s="5">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="5">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I9" s="5">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>29</v>
+      <c r="K9" s="5">
+        <v>10</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>30</v>
+      <c r="N9" s="5">
+        <v>12</v>
+      </c>
+      <c r="O9" s="5">
+        <v>12</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>20</v>
@@ -1288,38 +1300,38 @@
       <c r="S9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>31</v>
+      <c r="T9" s="5">
+        <v>13</v>
+      </c>
+      <c r="U9" s="5">
+        <v>13</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W9" s="5">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="X9" s="5">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC9" s="5">
-        <v>124</v>
+        <v>332</v>
       </c>
       <c r="AD9" s="5">
-        <v>124</v>
+        <v>332</v>
       </c>
       <c r="AE9" s="5" t="s">
         <v>20</v>
@@ -1334,10 +1346,10 @@
         <v>20</v>
       </c>
       <c r="AI9" s="5">
-        <v>240</v>
+        <v>628</v>
       </c>
       <c r="AJ9" s="5">
-        <v>240</v>
+        <v>628</v>
       </c>
       <c r="AK9" s="5" t="s">
         <v>20</v>
@@ -1346,46 +1358,46 @@
     <row r="10" spans="1:38">
       <c r="A10" s="2"/>
       <c r="B10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5">
-        <v>3.37</v>
+        <v>5.64</v>
       </c>
       <c r="E10" s="5">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="F10" s="5">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="5">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="I10" s="5">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="5">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L10" s="5">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>25</v>
+      <c r="N10" s="5">
+        <v>12</v>
+      </c>
+      <c r="O10" s="5">
+        <v>12</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>20</v>
@@ -1400,37 +1412,37 @@
         <v>20</v>
       </c>
       <c r="T10" s="5">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="U10" s="5">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="V10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W10" s="5">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="X10" s="5">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="Y10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC10" s="5">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="AD10" s="5">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="AE10" s="5" t="s">
         <v>20</v>
@@ -1445,10 +1457,10 @@
         <v>20</v>
       </c>
       <c r="AI10" s="5">
-        <v>465</v>
+        <v>888</v>
       </c>
       <c r="AJ10" s="5">
-        <v>465</v>
+        <v>888</v>
       </c>
       <c r="AK10" s="5" t="s">
         <v>20</v>
@@ -1457,92 +1469,92 @@
     <row r="11" spans="1:38">
       <c r="A11" s="2"/>
       <c r="B11" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5">
-        <v>2.87</v>
+        <v>6.76</v>
       </c>
       <c r="E11" s="5">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="F11" s="5">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="5">
+        <v>306</v>
+      </c>
+      <c r="I11" s="5">
+        <v>306</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="5">
+        <v>28</v>
+      </c>
+      <c r="L11" s="5">
+        <v>28</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="5">
+        <v>11</v>
+      </c>
+      <c r="O11" s="5">
+        <v>11</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="5">
+        <v>22</v>
+      </c>
+      <c r="U11" s="5">
+        <v>22</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="W11" s="5">
+        <v>167</v>
+      </c>
+      <c r="X11" s="5">
+        <v>167</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC11" s="5">
         <v>134</v>
       </c>
-      <c r="I11" s="5">
+      <c r="AD11" s="5">
         <v>134</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="5">
-        <v>22</v>
-      </c>
-      <c r="L11" s="5">
-        <v>22</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="W11" s="5">
-        <v>56</v>
-      </c>
-      <c r="X11" s="5">
-        <v>56</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC11" s="5">
-        <v>41</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>41</v>
-      </c>
       <c r="AE11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1556,10 +1568,10 @@
         <v>20</v>
       </c>
       <c r="AI11" s="5">
-        <v>301</v>
+        <v>785</v>
       </c>
       <c r="AJ11" s="5">
-        <v>301</v>
+        <v>785</v>
       </c>
       <c r="AK11" s="5" t="s">
         <v>20</v>
@@ -1568,109 +1580,109 @@
     <row r="12" spans="1:38">
       <c r="A12" s="2"/>
       <c r="B12" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D12" s="5">
-        <v>5.62</v>
+        <v>11.57</v>
       </c>
       <c r="E12" s="5">
-        <v>216</v>
+        <v>446</v>
       </c>
       <c r="F12" s="5">
-        <v>216</v>
+        <v>446</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="5">
-        <v>355</v>
+        <v>777</v>
       </c>
       <c r="I12" s="5">
-        <v>355</v>
+        <v>777</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="5">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="L12" s="5">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N12" s="5">
+        <v>61</v>
+      </c>
+      <c r="O12" s="5">
+        <v>61</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="T12" s="5">
+        <v>102</v>
+      </c>
+      <c r="U12" s="5">
+        <v>102</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="W12" s="5">
+        <v>532</v>
+      </c>
+      <c r="X12" s="5">
+        <v>532</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>293</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>293</v>
+      </c>
+      <c r="AE12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="O12" s="5">
+      <c r="AJ12" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="T12" s="5">
-        <v>62</v>
-      </c>
-      <c r="U12" s="5">
-        <v>62</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="W12" s="5">
-        <v>198</v>
-      </c>
-      <c r="X12" s="5">
-        <v>198</v>
-      </c>
-      <c r="Y12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>155</v>
-      </c>
-      <c r="AD12" s="5">
-        <v>155</v>
-      </c>
-      <c r="AE12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AG12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AH12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ12" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="AK12" s="5" t="s">
         <v>20</v>
@@ -1679,28 +1691,28 @@
     <row r="13" spans="1:38">
       <c r="A13" s="2"/>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5">
-        <v>0.68</v>
+        <v>2.1</v>
       </c>
       <c r="E13" s="5">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F13" s="5">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>36</v>
+      <c r="H13" s="5">
+        <v>29</v>
+      </c>
+      <c r="I13" s="5">
+        <v>29</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>20</v>
@@ -1715,10 +1727,10 @@
         <v>20</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>20</v>
@@ -1733,19 +1745,19 @@
         <v>20</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="V13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W13" s="5">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="X13" s="5">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="Y13" s="5" t="s">
         <v>20</v>
@@ -1760,10 +1772,10 @@
         <v>20</v>
       </c>
       <c r="AC13" s="5">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="AD13" s="5">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="AE13" s="5" t="s">
         <v>20</v>
@@ -1778,10 +1790,10 @@
         <v>20</v>
       </c>
       <c r="AI13" s="5">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AJ13" s="5">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AK13" s="5" t="s">
         <v>20</v>
@@ -1790,73 +1802,73 @@
     <row r="14" spans="1:38">
       <c r="A14" s="2"/>
       <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>28</v>
+      </c>
+      <c r="F14" s="5">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5">
+        <v>47</v>
+      </c>
+      <c r="I14" s="5">
+        <v>47</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="T14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.77</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5">
-        <v>21</v>
-      </c>
-      <c r="I14" s="5">
-        <v>21</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="U14" s="5" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W14" s="5">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="X14" s="5">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y14" s="5" t="s">
         <v>20</v>
@@ -1870,14 +1882,14 @@
       <c r="AB14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AC14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD14" s="5" t="s">
-        <v>36</v>
+      <c r="AC14" s="5">
+        <v>12</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>11</v>
       </c>
       <c r="AE14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF14" s="5" t="s">
         <v>20</v>
@@ -1889,58 +1901,58 @@
         <v>20</v>
       </c>
       <c r="AI14" s="5">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="AJ14" s="5">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="AK14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:38">
       <c r="A15" s="2"/>
       <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5">
+        <v>7.53</v>
+      </c>
+      <c r="E15" s="5">
+        <v>246</v>
+      </c>
+      <c r="F15" s="5">
+        <v>246</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5">
+        <v>252</v>
+      </c>
+      <c r="I15" s="5">
+        <v>252</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="5">
-        <v>3.67</v>
-      </c>
-      <c r="E15" s="5">
-        <v>125</v>
-      </c>
-      <c r="F15" s="5">
-        <v>125</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5">
-        <v>120</v>
-      </c>
-      <c r="I15" s="5">
-        <v>120</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="L15" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>31</v>
+      <c r="N15" s="5">
+        <v>17</v>
+      </c>
+      <c r="O15" s="5">
+        <v>17</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>20</v>
@@ -1955,37 +1967,37 @@
         <v>20</v>
       </c>
       <c r="T15" s="5">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="U15" s="5">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="V15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W15" s="5">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="X15" s="5">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="Y15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z15" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC15" s="5">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AD15" s="5">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AE15" s="5" t="s">
         <v>20</v>
@@ -2000,10 +2012,10 @@
         <v>20</v>
       </c>
       <c r="AI15" s="5">
-        <v>443</v>
+        <v>864</v>
       </c>
       <c r="AJ15" s="5">
-        <v>443</v>
+        <v>864</v>
       </c>
       <c r="AK15" s="5" t="s">
         <v>20</v>
@@ -2018,31 +2030,31 @@
         <v>47</v>
       </c>
       <c r="D16" s="5">
-        <v>5.18</v>
+        <v>11.79</v>
       </c>
       <c r="E16" s="5">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F16" s="5">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="5">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="I16" s="5">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>20</v>
@@ -2066,19 +2078,19 @@
         <v>20</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="V16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W16" s="5">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="X16" s="5">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Y16" s="5" t="s">
         <v>20</v>
@@ -2093,10 +2105,10 @@
         <v>20</v>
       </c>
       <c r="AC16" s="5">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="AD16" s="5">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="AE16" s="5" t="s">
         <v>20</v>
@@ -2111,10 +2123,10 @@
         <v>20</v>
       </c>
       <c r="AI16" s="5">
-        <v>208</v>
+        <v>489</v>
       </c>
       <c r="AJ16" s="5">
-        <v>208</v>
+        <v>489</v>
       </c>
       <c r="AK16" s="5" t="s">
         <v>20</v>
@@ -2129,40 +2141,40 @@
         <v>49</v>
       </c>
       <c r="D17" s="5">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="E17" s="5">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="F17" s="5">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="I17" s="5">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K17" s="5">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L17" s="5">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>29</v>
+      <c r="N17" s="5">
+        <v>12</v>
+      </c>
+      <c r="O17" s="5">
+        <v>12</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>20</v>
@@ -2177,19 +2189,19 @@
         <v>20</v>
       </c>
       <c r="T17" s="5">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="U17" s="5">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="V17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W17" s="5">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="X17" s="5">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="Y17" s="5" t="s">
         <v>20</v>
@@ -2204,10 +2216,10 @@
         <v>20</v>
       </c>
       <c r="AC17" s="5">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="AD17" s="5">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="AE17" s="5" t="s">
         <v>20</v>
@@ -2222,10 +2234,10 @@
         <v>20</v>
       </c>
       <c r="AI17" s="5">
-        <v>261</v>
+        <v>626</v>
       </c>
       <c r="AJ17" s="5">
-        <v>261</v>
+        <v>626</v>
       </c>
       <c r="AK17" s="5" t="s">
         <v>20</v>
@@ -2240,40 +2252,40 @@
         <v>51</v>
       </c>
       <c r="D18" s="5">
-        <v>2.86</v>
+        <v>8.14</v>
       </c>
       <c r="E18" s="5">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="F18" s="5">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="5">
-        <v>215</v>
+        <v>638</v>
       </c>
       <c r="I18" s="5">
-        <v>215</v>
+        <v>638</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>25</v>
+      <c r="K18" s="5">
+        <v>23</v>
+      </c>
+      <c r="L18" s="5">
+        <v>23</v>
       </c>
       <c r="M18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N18" s="5">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O18" s="5">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>20</v>
@@ -2288,19 +2300,19 @@
         <v>20</v>
       </c>
       <c r="T18" s="5">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="U18" s="5">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="V18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W18" s="5">
-        <v>137</v>
+        <v>422</v>
       </c>
       <c r="X18" s="5">
-        <v>137</v>
+        <v>422</v>
       </c>
       <c r="Y18" s="5" t="s">
         <v>20</v>
@@ -2315,10 +2327,10 @@
         <v>20</v>
       </c>
       <c r="AC18" s="5">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="AD18" s="5">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="AE18" s="5" t="s">
         <v>20</v>
@@ -2332,11 +2344,11 @@
       <c r="AH18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AI18" s="5">
-        <v>553</v>
-      </c>
-      <c r="AJ18" s="5">
-        <v>553</v>
+      <c r="AI18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ18" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="AK18" s="5" t="s">
         <v>20</v>
@@ -2345,46 +2357,46 @@
     <row r="19" spans="1:38">
       <c r="A19" s="2"/>
       <c r="B19" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>29</v>
+        <v>2</v>
+      </c>
+      <c r="E19" s="5">
+        <v>15</v>
+      </c>
+      <c r="F19" s="5">
+        <v>15</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>30</v>
+      <c r="H19" s="5">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <v>20</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>20</v>
@@ -2399,19 +2411,19 @@
         <v>20</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W19" s="5">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="X19" s="5">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="Y19" s="5" t="s">
         <v>20</v>
@@ -2426,10 +2438,10 @@
         <v>20</v>
       </c>
       <c r="AC19" s="5">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="AD19" s="5">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="AE19" s="5" t="s">
         <v>20</v>
@@ -2444,10 +2456,10 @@
         <v>20</v>
       </c>
       <c r="AI19" s="5">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="AJ19" s="5">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="AK19" s="5" t="s">
         <v>20</v>
@@ -2456,46 +2468,46 @@
     <row r="20" spans="1:38">
       <c r="A20" s="2"/>
       <c r="B20" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5">
-        <v>5.13</v>
+        <v>8.68</v>
       </c>
       <c r="E20" s="5">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="F20" s="5">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="5">
-        <v>290</v>
+        <v>458</v>
       </c>
       <c r="I20" s="5">
-        <v>290</v>
+        <v>458</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>52</v>
+      <c r="K20" s="5">
+        <v>18</v>
+      </c>
+      <c r="L20" s="5">
+        <v>18</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>30</v>
+      <c r="N20" s="5">
+        <v>12</v>
+      </c>
+      <c r="O20" s="5">
+        <v>12</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>20</v>
@@ -2510,55 +2522,55 @@
         <v>20</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="U20" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="V20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W20" s="5">
+        <v>157</v>
+      </c>
+      <c r="X20" s="5">
+        <v>157</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>884</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>884</v>
+      </c>
+      <c r="AE20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="X20" s="5">
+      <c r="AJ20" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="Y20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>272</v>
-      </c>
-      <c r="AD20" s="5">
-        <v>272</v>
-      </c>
-      <c r="AE20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AH20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI20" s="5">
-        <v>664</v>
-      </c>
-      <c r="AJ20" s="5">
-        <v>664</v>
       </c>
       <c r="AK20" s="5" t="s">
         <v>20</v>
@@ -2567,28 +2579,28 @@
     <row r="21" spans="1:38">
       <c r="A21" s="2"/>
       <c r="B21" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="5">
-        <v>12.15</v>
+        <v>25.23</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="5">
-        <v>177</v>
+        <v>364</v>
       </c>
       <c r="I21" s="5">
-        <v>177</v>
+        <v>364</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>20</v>
@@ -2647,11 +2659,11 @@
       <c r="AB21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AC21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD21" s="5" t="s">
-        <v>26</v>
+      <c r="AC21" s="5">
+        <v>17</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>17</v>
       </c>
       <c r="AE21" s="5" t="s">
         <v>20</v>
@@ -2666,10 +2678,10 @@
         <v>20</v>
       </c>
       <c r="AI21" s="5">
-        <v>184</v>
+        <v>392</v>
       </c>
       <c r="AJ21" s="5">
-        <v>184</v>
+        <v>392</v>
       </c>
       <c r="AK21" s="5" t="s">
         <v>20</v>
@@ -2678,28 +2690,28 @@
     <row r="22" spans="1:38">
       <c r="A22" s="2"/>
       <c r="B22" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" s="5">
-        <v>0.94</v>
+        <v>1.84</v>
       </c>
       <c r="E22" s="5">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F22" s="5">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="5">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I22" s="5">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>20</v>
@@ -2732,19 +2744,19 @@
         <v>20</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="V22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="X22" s="5" t="s">
-        <v>25</v>
+      <c r="W22" s="5">
+        <v>17</v>
+      </c>
+      <c r="X22" s="5">
+        <v>17</v>
       </c>
       <c r="Y22" s="5" t="s">
         <v>20</v>
@@ -2759,10 +2771,10 @@
         <v>20</v>
       </c>
       <c r="AC22" s="5">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AD22" s="5">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE22" s="5" t="s">
         <v>20</v>
@@ -2777,10 +2789,10 @@
         <v>20</v>
       </c>
       <c r="AI22" s="5">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="AJ22" s="5">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="AK22" s="5" t="s">
         <v>20</v>
@@ -2789,13 +2801,13 @@
     <row r="23" spans="1:38">
       <c r="A23" s="2"/>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" s="5">
-        <v>0.64</v>
+        <v>4.22</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>20</v>
@@ -2806,11 +2818,11 @@
       <c r="G23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>29</v>
+      <c r="H23" s="5">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <v>20</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>20</v>
@@ -2843,19 +2855,19 @@
         <v>20</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y23" s="5" t="s">
         <v>20</v>
@@ -2870,10 +2882,10 @@
         <v>20</v>
       </c>
       <c r="AC23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE23" s="5" t="s">
         <v>20</v>
@@ -2887,11 +2899,11 @@
       <c r="AH23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AI23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ23" s="5" t="s">
-        <v>30</v>
+      <c r="AI23" s="5">
+        <v>23</v>
+      </c>
+      <c r="AJ23" s="5">
+        <v>23</v>
       </c>
       <c r="AK23" s="5" t="s">
         <v>20</v>
@@ -2900,28 +2912,28 @@
     <row r="24" spans="1:38">
       <c r="A24" s="2"/>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="5">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>25</v>
+      <c r="H24" s="5">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5">
+        <v>15</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>20</v>
@@ -2936,10 +2948,10 @@
         <v>20</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>20</v>
@@ -2954,19 +2966,19 @@
         <v>20</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>36</v>
+      <c r="W24" s="5">
+        <v>17</v>
+      </c>
+      <c r="X24" s="5">
+        <v>17</v>
       </c>
       <c r="Y24" s="5" t="s">
         <v>20</v>
@@ -2981,10 +2993,10 @@
         <v>20</v>
       </c>
       <c r="AC24" s="5">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="AD24" s="5">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="AE24" s="5" t="s">
         <v>20</v>
@@ -2999,10 +3011,10 @@
         <v>20</v>
       </c>
       <c r="AI24" s="5">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="AJ24" s="5">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="AK24" s="5" t="s">
         <v>20</v>
@@ -3011,46 +3023,46 @@
     <row r="25" spans="1:38">
       <c r="A25" s="2"/>
       <c r="B25" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25" s="5">
-        <v>3.87</v>
+        <v>6.42</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I25" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>20</v>
@@ -3065,10 +3077,10 @@
         <v>20</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V25" s="5" t="s">
         <v>20</v>
@@ -3092,10 +3104,10 @@
         <v>20</v>
       </c>
       <c r="AC25" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD25" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE25" s="5" t="s">
         <v>20</v>
@@ -3110,10 +3122,10 @@
         <v>20</v>
       </c>
       <c r="AI25" s="5">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AJ25" s="5">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AK25" s="5" t="s">
         <v>20</v>
@@ -3122,28 +3134,28 @@
     <row r="26" spans="1:38">
       <c r="A26" s="2"/>
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D26" s="5">
-        <v>2.85</v>
+        <v>4.78</v>
       </c>
       <c r="E26" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F26" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="5">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="I26" s="5">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>20</v>
@@ -3158,10 +3170,10 @@
         <v>20</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>20</v>
@@ -3176,19 +3188,19 @@
         <v>20</v>
       </c>
       <c r="T26" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="V26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W26" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="X26" s="5" t="s">
-        <v>25</v>
+      <c r="W26" s="5">
+        <v>21</v>
+      </c>
+      <c r="X26" s="5">
+        <v>21</v>
       </c>
       <c r="Y26" s="5" t="s">
         <v>20</v>
@@ -3203,10 +3215,10 @@
         <v>20</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AD26" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AE26" s="5" t="s">
         <v>20</v>
@@ -3221,10 +3233,10 @@
         <v>20</v>
       </c>
       <c r="AI26" s="5">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="AJ26" s="5">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="AK26" s="5" t="s">
         <v>20</v>
@@ -3233,46 +3245,46 @@
     <row r="27" spans="1:38">
       <c r="A27" s="2"/>
       <c r="B27" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D27" s="5">
-        <v>2.71</v>
+        <v>5.94</v>
       </c>
       <c r="E27" s="5">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F27" s="5">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="5">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="I27" s="5">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>31</v>
+      <c r="N27" s="5">
+        <v>14</v>
+      </c>
+      <c r="O27" s="5">
+        <v>14</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>20</v>
@@ -3286,20 +3298,20 @@
       <c r="S27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>52</v>
+      <c r="T27" s="5">
+        <v>19</v>
+      </c>
+      <c r="U27" s="5">
+        <v>19</v>
       </c>
       <c r="V27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W27" s="5">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="X27" s="5">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="Y27" s="5" t="s">
         <v>20</v>
@@ -3314,10 +3326,10 @@
         <v>20</v>
       </c>
       <c r="AC27" s="5">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="AD27" s="5">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="AE27" s="5" t="s">
         <v>20</v>
@@ -3332,10 +3344,10 @@
         <v>20</v>
       </c>
       <c r="AI27" s="5">
-        <v>176</v>
+        <v>427</v>
       </c>
       <c r="AJ27" s="5">
-        <v>176</v>
+        <v>427</v>
       </c>
       <c r="AK27" s="5" t="s">
         <v>20</v>
@@ -3344,46 +3356,46 @@
     <row r="28" spans="1:38">
       <c r="A28" s="2"/>
       <c r="B28" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D28" s="5">
-        <v>5.35</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>30</v>
+        <v>18.31</v>
+      </c>
+      <c r="E28" s="5">
+        <v>19</v>
+      </c>
+      <c r="F28" s="5">
+        <v>19</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="5">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="I28" s="5">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>20</v>
@@ -3398,19 +3410,19 @@
         <v>20</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="V28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W28" s="5" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="X28" s="5" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="Y28" s="5" t="s">
         <v>20</v>
@@ -3424,11 +3436,11 @@
       <c r="AB28" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AC28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD28" s="5" t="s">
-        <v>36</v>
+      <c r="AC28" s="5">
+        <v>16</v>
+      </c>
+      <c r="AD28" s="5">
+        <v>16</v>
       </c>
       <c r="AE28" s="5" t="s">
         <v>20</v>
@@ -3443,10 +3455,10 @@
         <v>20</v>
       </c>
       <c r="AI28" s="5">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="AJ28" s="5">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="AK28" s="5" t="s">
         <v>20</v>
@@ -3455,109 +3467,109 @@
     <row r="29" spans="1:38">
       <c r="A29" s="2"/>
       <c r="B29" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D29" s="5">
-        <v>68.27</v>
-      </c>
-      <c r="E29" s="5">
-        <v>978</v>
-      </c>
-      <c r="F29" s="5">
-        <v>978</v>
+        <v>154.75</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K29" s="5">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="L29" s="5">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N29" s="5">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="O29" s="5">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="T29" s="5">
-        <v>223</v>
+        <v>428</v>
       </c>
       <c r="U29" s="5">
-        <v>223</v>
+        <v>428</v>
       </c>
       <c r="V29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W29" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Y29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z29" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA29" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC29" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AD29" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AE29" s="5" t="s">
         <v>22</v>
       </c>
       <c r="AF29" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AI29" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AJ29" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AK29" s="5" t="s">
         <v>22</v>
@@ -3565,110 +3577,110 @@
     </row>
     <row r="30" spans="1:38">
       <c r="A30" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D30" s="5">
-        <v>68.27</v>
-      </c>
-      <c r="E30" s="5">
-        <v>978</v>
-      </c>
-      <c r="F30" s="5">
-        <v>978</v>
+        <v>154.75</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K30" s="5">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="L30" s="5">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="N30" s="5">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="O30" s="5">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R30" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="T30" s="5">
-        <v>223</v>
+        <v>428</v>
       </c>
       <c r="U30" s="5">
-        <v>223</v>
+        <v>428</v>
       </c>
       <c r="V30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W30" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Y30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="Z30" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA30" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AC30" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AD30" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AE30" s="5" t="s">
         <v>22</v>
       </c>
       <c r="AF30" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG30" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AI30" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AJ30" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AK30" s="5" t="s">
         <v>22</v>
